--- a/Vf/TABLE_4_5/Table_5_PanelA_MIDAS.xlsx
+++ b/Vf/TABLE_4_5/Table_5_PanelA_MIDAS.xlsx
@@ -447,16 +447,16 @@
         <v>-0.9</v>
       </c>
       <c r="B2" t="n">
-        <v>1.048676491949402</v>
+        <v>1.047383194748607</v>
       </c>
       <c r="C2" t="n">
-        <v>1.050237076101406</v>
+        <v>1.047264642468214</v>
       </c>
       <c r="D2" t="n">
-        <v>1.038723844344958</v>
+        <v>1.03624257663946</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9147013076704982</v>
+        <v>0.9134390791805925</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>-0.5</v>
       </c>
       <c r="B3" t="n">
-        <v>1.047410044030334</v>
+        <v>1.04660230221494</v>
       </c>
       <c r="C3" t="n">
-        <v>1.123361981543008</v>
+        <v>1.121814359934371</v>
       </c>
       <c r="D3" t="n">
-        <v>1.129016282134369</v>
+        <v>1.128057289553508</v>
       </c>
       <c r="E3" t="n">
-        <v>1.021067816440899</v>
+        <v>1.02077062183039</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1.043234044517219</v>
+        <v>1.043336593463487</v>
       </c>
       <c r="C4" t="n">
-        <v>1.122443564308768</v>
+        <v>1.120916481003285</v>
       </c>
       <c r="D4" t="n">
-        <v>1.124707770298013</v>
+        <v>1.1212822844358</v>
       </c>
       <c r="E4" t="n">
-        <v>1.036951252978058</v>
+        <v>1.036302636186864</v>
       </c>
     </row>
     <row r="5">
@@ -501,13 +501,13 @@
         <v>1.032795250397929</v>
       </c>
       <c r="C5" t="n">
-        <v>1.115702010023846</v>
+        <v>1.113308734819361</v>
       </c>
       <c r="D5" t="n">
-        <v>1.115395329457821</v>
+        <v>1.113505989641775</v>
       </c>
       <c r="E5" t="n">
-        <v>1.04750369311725</v>
+        <v>1.046847133311732</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>0.95</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9563726212146051</v>
+        <v>0.9280196814332935</v>
       </c>
       <c r="C6" t="n">
-        <v>1.053638780140705</v>
+        <v>1.050928489880385</v>
       </c>
       <c r="D6" t="n">
-        <v>1.082470143422389</v>
+        <v>1.080772350037598</v>
       </c>
       <c r="E6" t="n">
-        <v>1.080213049274584</v>
+        <v>1.078597653207427</v>
       </c>
     </row>
   </sheetData>
